--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/MISSOURI_2023.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2023/MISSOURI_2023.xlsx
@@ -4974,7 +4974,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C257">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>General Escobedo</t>
+          <t>Gral. Escobedo</t>
         </is>
       </c>
       <c r="C561">
